--- a/九龙-旺角-利奥坊．凯岸/利奥坊．凯岸_销控明细表.xlsx
+++ b/九龙-旺角-利奥坊．凯岸/利奥坊．凯岸_销控明细表.xlsx
@@ -14102,7 +14102,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>5831040</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>23512</v>
+        <v>23418</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>5831040</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>23512</v>
+        <v>23418</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -34714,9 +34714,9 @@
       </c>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t>J | 248呎 (1房)
+          <t>J | 249呎 (1房)
 $583万
-$23,512/呎
+$23,418/呎
 (18年-07月-06日)</t>
         </is>
       </c>
